--- a/01_analyses_states/Karnataka/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Karnataka/results/SoIB_summaries.xlsx
@@ -509,10 +509,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="E2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -523,13 +523,13 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>32.4</v>
+        <v>33.3</v>
       </c>
       <c r="E3">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -540,13 +540,13 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4">
-        <v>32.4</v>
+        <v>33.3</v>
       </c>
       <c r="E4">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -560,10 +560,10 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="E5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -571,16 +571,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>9</v>
       </c>
       <c r="D6">
-        <v>10.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E6">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -588,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C7">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C8">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -713,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,10 +750,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -761,10 +761,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C4">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -807,16 +807,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>69.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>76.3</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -827,13 +827,13 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="D3">
         <v>23</v>
       </c>
       <c r="E3">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
     </row>
   </sheetData>
